--- a/data/gravel/Brodie Mega Tour 2.0 2025.xlsx
+++ b/data/gravel/Brodie Mega Tour 2.0 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1508D50E-727C-474D-8C04-105F646D0DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358408B1-EDAD-204D-B9AA-77BF141CFB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6140" yWindow="800" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -368,7 +368,13 @@
     <t>carbon</t>
   </si>
   <si>
-    <t>a8:f31</t>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f33</t>
   </si>
 </sst>
 </file>
@@ -732,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -796,7 +802,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1112,488 +1118,522 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>111</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>20</v>
+        <v>112</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="1">
-        <v>40</v>
-      </c>
-      <c r="D25" s="1">
-        <v>50</v>
-      </c>
-      <c r="E25" s="1">
-        <v>50</v>
-      </c>
-      <c r="F25" s="1">
-        <v>60</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="4">
-        <v>700</v>
-      </c>
-      <c r="D27" s="4">
-        <v>700</v>
-      </c>
-      <c r="E27" s="4">
-        <v>700</v>
-      </c>
-      <c r="F27" s="4">
-        <v>700</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="C27" s="1">
+        <v>40</v>
+      </c>
+      <c r="D27" s="1">
+        <v>50</v>
+      </c>
+      <c r="E27" s="1">
+        <v>50</v>
+      </c>
+      <c r="F27" s="1">
+        <v>60</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="4">
-        <v>2.6</v>
-      </c>
-      <c r="D28" s="4">
-        <v>2.6</v>
-      </c>
-      <c r="E28" s="4">
-        <v>2.6</v>
-      </c>
-      <c r="F28" s="4">
-        <v>2.6</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
+        <v>23</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="E29" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2.6</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C29" s="4">
+        <v>700</v>
+      </c>
+      <c r="D29" s="4">
+        <v>700</v>
+      </c>
+      <c r="E29" s="4">
+        <v>700</v>
+      </c>
+      <c r="F29" s="4">
+        <v>700</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="D30" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="E30" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="F30" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="F31" s="1">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="1">
-        <f>2.54*C32</f>
+      <c r="C32" s="1">
+        <f>2.54*C34</f>
         <v>157.47999999999999</v>
       </c>
-      <c r="D30" s="1">
-        <f t="shared" ref="D30:F31" si="1">2.54*D32</f>
+      <c r="D32" s="1">
+        <f t="shared" ref="D32:F33" si="1">2.54*D34</f>
         <v>167.64000000000001</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E32" s="1">
         <f t="shared" si="1"/>
         <v>175.26</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F32" s="1">
         <f t="shared" si="1"/>
         <v>182.88</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="1">
-        <f>2.54*C33</f>
+      <c r="C33" s="1">
+        <f>2.54*C35</f>
         <v>170.18</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D33" s="1">
         <f t="shared" si="1"/>
         <v>177.8</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E33" s="1">
         <f t="shared" si="1"/>
         <v>185.42000000000002</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F33" s="1">
         <f t="shared" si="1"/>
         <v>193.04</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="1">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C34" s="1">
         <v>62</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D34" s="1">
         <v>66</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E34" s="1">
         <v>69</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F34" s="1">
         <v>72</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="1">
-        <v>67</v>
-      </c>
-      <c r="D33" s="1">
-        <v>70</v>
-      </c>
-      <c r="E33" s="1">
-        <v>73</v>
-      </c>
-      <c r="F33" s="1">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>108</v>
+        <v>30</v>
+      </c>
+      <c r="C35" s="1">
+        <v>67</v>
+      </c>
+      <c r="D35" s="1">
+        <v>70</v>
+      </c>
+      <c r="E35" s="1">
+        <v>73</v>
+      </c>
+      <c r="F35" s="1">
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="1">
-        <v>6061</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="1">
+        <v>6061</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="1">
-        <v>2.6</v>
+        <v>32</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B42" s="1">
-        <v>120</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B44" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="1">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="1">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
+      </c>
+      <c r="B48" s="1">
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
+      </c>
+      <c r="B49" s="1">
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>43</v>
+        <v>77</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="1">
-        <v>31.6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="B58" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B60" s="1">
-        <v>180</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B61" s="1">
-        <v>180</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="B62" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>94</v>
+        <v>49</v>
+      </c>
+      <c r="B63" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B67" s="1">
-        <v>4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B68" s="1">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B69" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B70" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>90</v>
+        <v>58</v>
+      </c>
+      <c r="B72" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75" s="1">
-        <v>2599</v>
+        <v>61</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>80</v>
+        <v>63</v>
+      </c>
+      <c r="B77" s="1">
+        <v>2599</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B80" s="6" t="s">
         <v>81</v>
       </c>
     </row>
